--- a/outputs/416-27.xlsx
+++ b/outputs/416-27.xlsx
@@ -20,27 +20,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
-    <t xml:space="preserve">Sub Del_Blanks()</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dim LR As Long</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LR = Range("A" &amp; Rows.Count).End(xlUp).Row</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Range("A4:A" &amp; LR).AutoFilter Field:=1, Criteria1:="="</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Range("A4:A" &amp; LR).SpecialCells(xlCellTypeVisible).EntireRow.Delete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Range("A4:A" &amp; LR).AutoFilter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">End Sub</t>
+    <t xml:space="preserve">Ref</t>
   </si>
   <si>
     <t xml:space="preserve">LKP103</t>
@@ -137,16 +119,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -342,105 +328,93 @@
   <dimension ref="A1:G27"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.57"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>5</v>
-      </c>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2"/>
+      <c r="A9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2"/>
+      <c r="A20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
-        <v>7</v>
-      </c>
+      <c r="A21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="A23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="A24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="26" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/outputs/416-27.xlsx
+++ b/outputs/416-27.xlsx
@@ -336,86 +336,41 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.57"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3"/>
-    </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3"/>
-    </row>
-    <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3"/>
-    </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3"/>
-    </row>
-    <row r="23" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3"/>
-    </row>
-    <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3"/>
-    </row>
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="23" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="25" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="26" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="27" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
